--- a/output/amazon_2026-06-30.xlsx
+++ b/output/amazon_2026-06-30.xlsx
@@ -477,16 +477,16 @@
         <v>Apple iPhone 12 Pro 5G (128GB, Blue) - Excellent</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.amazon.com.au/dp/B098P7QYFL</v>
+        <v>https://www.amazon.com.au/dp/B0968GVWLZ</v>
       </c>
       <c r="D3" t="str">
-        <v>128GB, 128 GB, 128GB, 128 GB | Pacific Blue</v>
+        <v>128GB, 128 GB, 128GB, 128 GB | Gold</v>
       </c>
       <c r="E3" t="str">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="F3" t="str">
-        <v>iPhone 12 Pro 128GB Pacific Blue (Renewed)</v>
+        <v>Filter by</v>
       </c>
       <c r="G3" t="str">
         <v>0.5</v>
@@ -501,7 +501,7 @@
         <v>Excellent</v>
       </c>
       <c r="K3" t="str">
-        <v>https://www.amazon.com.au/dp/B098P7QYFL</v>
+        <v>https://www.amazon.com.au/dp/B0968GVWLZ</v>
       </c>
     </row>
     <row r="4">
@@ -609,7 +609,7 @@
         <v/>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
         <v>iPhone12Pro5G128GBSilv-RD-VR-EXD-AU</v>
       </c>
@@ -617,34 +617,41 @@
         <v>Apple iPhone 12 Pro 5G (128GB, Silver) - Excellent</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>https://www.amazon.com.au/dp/B0968GVWLZ</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>128GB, 128 GB, 128GB, 128 GB | Gold</v>
       </c>
       <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
+        <v>414</v>
+      </c>
+      <c r="F7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Product summary presents key product information       Keyboard shortcut  
+                        Shift
+                        +
+                         Alt
+                        +
+                        opt
+                        +
+                        D</v>
       </c>
       <c r="G7" t="str">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H7" t="str">
-        <v>no_match</v>
+        <v>matched</v>
       </c>
       <c r="I7" t="str">
         <v/>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>Excellent</v>
       </c>
       <c r="K7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
+        <v>https://www.amazon.com.au/dp/B0968GVWLZ</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
       <c r="A8" t="str">
         <v>iP12Pro5G256GBBlue-RD-VR-EXD-AU</v>
       </c>
@@ -652,31 +659,38 @@
         <v>Apple iPhone 12 Pro 5G (256GB, Blue) - Excellent</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>https://www.amazon.com.au/dp/B0968GVWLZ</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>128GB, 128 GB, 128GB, 128 GB | Gold</v>
       </c>
       <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
+        <v>414</v>
+      </c>
+      <c r="F8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Product summary presents key product information       Keyboard shortcut  
+                        Shift
+                        +
+                         Alt
+                        +
+                        opt
+                        +
+                        D</v>
       </c>
       <c r="G8" t="str">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H8" t="str">
-        <v>no_match</v>
+        <v>matched</v>
       </c>
       <c r="I8" t="str">
         <v/>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>Excellent</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>https://www.amazon.com.au/dp/B0968GVWLZ</v>
       </c>
     </row>
     <row r="9">
